--- a/ablation_study.xlsx
+++ b/ablation_study.xlsx
@@ -425,26 +425,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Full LSTM</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PCA+LSTM</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Test Loss (MSE)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
@@ -453,128 +468,178 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>window p</t>
+          <t>(α) RMSE one-step (mean)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>0.0001270850043511018</v>
       </c>
       <c r="C2" t="n">
-        <v>6.211416840700221e-06</v>
-      </c>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
+        <v>0.006428921595215797</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>window p</t>
+          <t>(α) RMSE autoregressive (mean)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>0.004175374284386635</v>
       </c>
       <c r="C3" t="n">
-        <v>6.364442101428345e-06</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
+        <v>0.006876632571220398</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>window p</t>
+          <t>(β) RMSE auto at t=20s</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>0.006997324991971254</v>
       </c>
       <c r="C4" t="n">
-        <v>3.719559669284373e-06</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
+        <v>0.006392982322722673</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hidden size</t>
+          <t>(γ) State space dimension</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>7.300626703391604e-06</v>
-      </c>
-      <c r="D5" t="b">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hidden size</t>
+          <t>(γ) Explained variance (%)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
-        <v>6.159695252680931e-06</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
+        <v>99.48</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hidden size</t>
+          <t>(δ) Model parameters</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>128</v>
+        <v>20362</v>
       </c>
       <c r="C7" t="n">
-        <v>3.119949531769007e-06</v>
-      </c>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
+        <v>18115</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>num layers</t>
+          <t>(δ) Training epochs</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>149</v>
       </c>
       <c r="C8" t="n">
-        <v>1.122250422920858e-06</v>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>num layers</t>
+          <t>(δ) Inference time per traj (s)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>0.5998109181722006</v>
       </c>
       <c r="C9" t="n">
-        <v>5.327923051956124e-06</v>
-      </c>
-      <c r="D9" t="b">
+        <v>0.5929810206095377</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>normalization</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>with norm</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>6.006548949440473e-06</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>normalization</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>without norm</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.137682769754241e-07</v>
+      </c>
+      <c r="G11" t="b">
         <v>0</v>
       </c>
     </row>
